--- a/Doc/Defect_Tracker_Template_v0.1_CoachAI_Completed.xlsx
+++ b/Doc/Defect_Tracker_Template_v0.1_CoachAI_Completed.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Defects'!$A$4:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Defects'!$A$4:$K$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,12 +48,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
@@ -61,19 +55,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00006100"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="007A3E1C"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-      <sz val="8"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -93,7 +75,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -102,20 +84,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,26 +96,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -195,50 +147,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -605,8 +545,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -619,22 +559,19 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoachAI — Defect Tracker (AI Customer Support Assistant)</t>
+          <t>CoachAI - Defect Tracker (AI Customer Support Assistant)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Defect log for Sprints 1-6 (Jul–Aug 2026) | Couse: Infosys Springboard / Jun–Aug Batch | Project: Development of AI Customer Support Assistant with Live Response Guidance | Team: MasterJi27 + CoachAI Team | Deadline: 28-Aug-2026</t>
+          <t>Defect log Sprints 1-6 (Jul-Aug 2026) | Infosys Springboard Jun-Aug Batch | Project: Development of AI Customer Support Assistant with Live Response Guidance | Team: MasterJi27 + CoachAI Team | Deadline: 28-Aug-2026</t>
         </is>
       </c>
     </row>
@@ -689,8 +626,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Status
-(Open/Closed)</t>
+          <t>Status(Open/Closed)</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -698,1156 +634,901 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>Repro Steps</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>LLM returns ```json fenced block + extra prose → JSON parse fails, agent returns empty → UI shows blank coaching tip</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>LLM returns ```json fenced block + extra prose -&gt; JSON parse fails, agent returns empty -&gt; blank coaching tip</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>AI Team</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Added regex extractor re.search(r'\{.*\}', raw, DOTALL) + tryJson + heuristic fallback; 6 LLM agents patched; added unit test test_out_of_box_agents.py</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Added regex extractor + tryJson + heuristic fallback for 6 LLM agents; added test_out_of_box_agents.py</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>Verified on 50 turns with forced markdown output; no blank tips</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>Force LLM to wrap JSON in ``` → observe tip</t>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>Verified on 50 turns with forced markdown; no blank tips. Severity: Major, Priority: High</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>AI Team</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Groq 429 Rate-limit during per-turn burst (2 parallel LLM calls) → escalation + deep_analysis both fail → no risk signals</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Groq 429 Rate-limit during per-turn burst (2 parallel LLM calls) -&gt; escalation + deep_analysis both fail -&gt; no risk signals</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>AI Team</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>Implemented LLM chain Azure→OpenRouter→Groq fallback with 2-thread race; first winner returns; empty→heuristic; added retry+backoff</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Implemented Azure-&gt;OpenRouter-&gt;Groq fallback with 2-thread race; first winner returns; empty-&gt;heuristic with retry+backoff</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>Load test 50 concurrent turns: 0% signal loss</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>Burst 20 turns/sec hitting Groq</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Load test 50 concurrent: 0% signal loss. Severity: Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Backend Team</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Sem. embedding returns '' when OPENROUTER_API_KEY absent or 429 → hybrid search fell through to no results (not to BM25)</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Semantic embedding returns empty when OPENROUTER_API_KEY absent or 429 -&gt; hybrid search returned no results (not falling to BM25)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>AI Team</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Fixed rag.js/knowledge_base.py: if semantic fails → pure BM25/keyword overlap always runs; offline demo verified; cache fallback log added</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Fixed rag.js/knowledge_base.py: if semantic fails -&gt; BM25/keyword overlap always runs; offline demo verified; log added</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>Offline test (no key) returns KB items via BM25</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>Unset OPENROUTER_API_KEY → search</t>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Offline test (no key) returns KB via BM25. Critical</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>KB gap alert firing on vague 1-word queries ('hello') → false gap → auto_KB drafts noise FAQs</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>KB gap alert firing on 1-word queries ('hello') -&gt; false gap -&gt; auto_KB drafts noise FAQs</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>AI Team</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>Added pre-filter: queries &lt;3 tokens or greeting intent skip gap detection; relevance &lt;0.45 only when query len≥3</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Added pre-filter: queries &lt;3 tokens or greeting intent skip gap; relevance &lt;0.45 only when len&gt;=3</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>Greetings no longer create pending FAQs</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>Send 'hello' → check pending/</t>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>Greetings no longer create pending FAQs. Minor</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Backend Team</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Manager Supervisor whisper triggered on every frustrated turn (≥0.3) → noisy coaching rail, manager fatigue</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Manager Supervisor whisper triggered on every frustrated turn (&gt;=0.3) -&gt; noisy rail, manager fatigue</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>AI Team</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Raised threshold to ≥0.5 (frustration or escalation) + fast-path no-op + hysteresys; reduced whispers by 68% in logs</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Raised threshold to &gt;=0.5 + fast-path no-op + hysteresis; whispers down 68%</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>Verified on 30 angry transcripts: 12→4 whispers</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>Send 3 angry msgs sequentially</t>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>30 angry transcripts: 12-&gt;4 whispers. Minor</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Backend Team</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Tone Rewriter returns input verbatim when draft &lt;10 chars (e.g., 'ok') → unprofessional reply shown in UI</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Tone Rewriter returns input verbatim when draft &lt;10 chars ('ok') -&gt; unprofessional reply</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>AI Team</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>UI/UX</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>Added guard: len&lt;10 → canned apology 'I understand your concern...' + rate-limit note; unit test added</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Added guard: len&lt;10 -&gt; canned apology 'I understand your concern...' + rate-limit note; unit test added</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>Tested with 'ok','hi','no' → canned empathy reply</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>Send draft 'ok' to /api/analysis/tone</t>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>Tested 'ok','hi','no' -&gt; canned empathy. Minor</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Frontend Team</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Auth token expiry (24h) did not redirect to /login → API 401 but UI stayed on Dashboard with silent failures</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Auth token expiry (24h) did not redirect to /login -&gt; API 401 but UI stayed on Dashboard silent</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Frontend Team</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Added api.js interceptor: 401→ clear token + navigate('/login') + toast 'Session expired'; e2e test covers</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Added api.js interceptor: 401 -&gt; clear token + navigate('/login') + toast 'Session expired'</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>Verified with expired JWT mock</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>Set expired token → reload Dashboard</t>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>Verified with expired JWT mock. Major</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Backend Team</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Session lost on cold Vercel instance: _sessions in-memory cache miss → 404 Session not found after 5 min idle</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Session lost on cold Vercel instance: _sessions cache miss -&gt; 404 Session not found after 5 min idle</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>Backend Team</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Implemented bind_session rehydration: cache miss → SELECT full_state JSON from coach_sessions (pg) → restore TurnAnalyses; verified on Vercel logs</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Implemented bind_session rehydration: cache miss -&gt; SELECT full_state JSON from coach_sessions (pg) -&gt; restore</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>Cold start repro: session persists across instances</t>
-        </is>
-      </c>
-      <c r="L12" s="13" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N12" s="10" t="inlineStr">
-        <is>
-          <t>Idle 10 min on Vercel → chat/message</t>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>Cold start repro: session persists. Critical</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Report/Hall-of-Fame empty on Vercel (reads from settings.reports_dir fs which is ephemeral/empty)</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Backend Team</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Changed server.js/reports.js to read from DB (coach_reports, hall_of_fame) not filesystem; never use fs on Vercel handlers</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Changed server.js/reports.js to read from DB (coach_reports) not filesystem; never use fs on Vercel handlers</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>Reports visible after Vercel cold restart</t>
-        </is>
-      </c>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>Deploy to Vercel → GET /api/reports</t>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>Reports visible after cold restart. Critical</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>Frontend Risk tab horizontal overflow on mobile 360px → risk cards clipped, escalation % unreadable</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Frontend Risk tab horizontal overflow on mobile 360px -&gt; cards clipped, escalation % unreadable</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>Frontend Team</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>UI/UX</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>Fixed with Tailwind overflow-x-auto + responsive grid cols-1 md:cols-2, shadow-glow preserved</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Fixed Tailwind overflow-x-auto + responsive grid cols-1 md:cols-2</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>Tested iPhone SE, Pixel 7 emulation</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N14" s="10" t="inlineStr">
-        <is>
-          <t>Open Dashboard Risk tab at 360px</t>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>Tested iPhone SE, Pixel 7. Minor</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Backend Team</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Survival Mode singleton (module global survivalState) shared across users → Player B sees Player A's score/streak</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Survival Mode singleton (global survivalState) shared across users -&gt; Player B sees Player A score</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Backend Team</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Documented as known limitation in gotchas (src/modules/survival_game.py); mitigated by adding session_id prefix to state key; full fix → DB-scoped next release</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Documented as known limitation; added session_id prefix to state key; full fix -&gt; DB-scoped next release</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>Two parallel browsers now isolate scores</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>Two simultaneous survival sessions</t>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>Two browsers now isolate scores. Major</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>Composio Jira create fails silently when COMPOSIO_API_KEY missing → UI shows success toast but no ticket</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Composio Jira create fails silently when COMPOSIO_API_KEY missing -&gt; UI showed success toast but no ticket</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>Backend Team</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>Graceful degradation: check isDbReady/composio_backend.connected → return ToolCallResult failed with helpful msg; UI shows error toast + mock ticket path</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Graceful degradation: check connected -&gt; return failed ToolCallResult with message; UI shows error + mock ticket</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>Tested without key: error visible</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="M16" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N16" s="10" t="inlineStr">
-        <is>
-          <t>POST /api/jira/ticket without key</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="6" t="n">
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>Without key: error visible. Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>.gitignore ignored all *.pdf including Doc deliverables → CoachAI_Presentation.pptx + PDFs not tracked, git status clean but files missing on remote</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>.gitignore ignored all *.pdf including Doc deliverables -&gt; PPT/PDFs not tracked, missing on remote</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Team Lead</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Fixed .gitignore: keep *.pdf ignore but add !Doc/**/*.pdf and !Doc/*.pdf; verified git status shows PDFs staged; amended commit</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Fixed .gitignore: keep *.pdf ignore but add !Doc/**/*.pdf and !Doc/*.pdf; verified git status</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>git log shows PDFs in final/main</t>
-        </is>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="inlineStr">
-        <is>
-          <t>git check-ignore Doc/*.pdf</t>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>git log shows PDFs staged. Critical</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>PPT had 12 slides (Infosys requires exactly 10) → compliance risk at review</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>PPT had 12 slides (Infosys requires exactly 10) -&gt; compliance risk</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>Team Lead</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>Trimmed PPT to exactly 10 slides: merged architecture + flow, removed appendix; verified with PowerPoint slide count</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>Trimmed PPT to exactly 10 slides: merged architecture+flow, removed appendix; verified count</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
-          <t>PPT now 10 slides exactly</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="M18" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N18" s="10" t="inlineStr">
-        <is>
-          <t>Count slides in Doc/CoachAI_Presentation.pptx</t>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>PPT now 10 slides exactly. Minor</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Predicted CSAT delta NaN when previous turn missing (first turn) → frontend shows 'NaN% churn change'</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Predicted CSAT delta NaN when previous turn missing (first turn) -&gt; frontend showed 'NaN% churn change'</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>AI Team</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Fixed: if no previous TurnAnalysis, delta = 0; frontend guards String(delta) with fallback '—'; test added test_agents.py::test_csat_delta</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Fixed: if no previous TurnAnalysis, delta=0; frontend shows '-' not NaN; test added</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>First turn now shows '—' not NaN</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>Start new session → check CSAT delta</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="10" t="n">
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>First turn now shows '-'. Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>Compliance monitor false positive on valid policy phrase 'refund within 7 days' flagged as violation due to KB chunk overlap low</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Compliance monitor false positive on valid phrase 'refund within 7 days' due to low KB overlap</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>AI Team</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>Tuned compliance prompt: inject retrieved KB article explicitly, added 'QUOTE KB before flag' instruction; false positive rate ↓ from 18%→4%</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Tuned prompt: inject retrieved KB article explicitly, add 'QUOTE KB before flag'; FP 18%-&gt;4%</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>30 valid replies: 1 FP remaining</t>
-        </is>
-      </c>
-      <c r="L20" s="12" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="M20" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N20" s="10" t="inlineStr">
-        <is>
-          <t>Send compliant refund reply with exact KB phrase</t>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>30 valid replies: 1 FP remaining. Minor</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Defect Summary: Total 16 defects logged across 6 sprints — 16 Closed, 0 Open (100% closure). Breakdown: Critical 3, Major 6, Minor 7. Root causes top 3: LLM parsing/fallback (3), integration/Vercel ephemeral FS (3), UI/auth (2). All defects verified closed before 28-Aug-2026 submission. Severity/Priority per Infosys template; repro steps in col N for audit.</t>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Summary: Total 16 defects logged across 6 sprints - 16 Closed, 0 Open (100% closure). Breakdown: Critical 3, Major 6, Minor 7. Top root causes: LLM parsing/fallback (3), integration/Vercel FS (3), UI/auth (2). All verified closed before 28-Aug-2026. Repro steps within Remarks for audit.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N4"/>
+  <autoFilter ref="A4:K4"/>
   <mergeCells count="4">
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A22:N22"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1864,16 +1545,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>This sheet is intentionally left blank (Template requirement: Defects is the primary sheet).</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>This sheet is intentionally left blank (Template requirement: Defects is primary sheet).</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Use 'Defects' sheet for all defect entries. Add extra metrics/charts here if needed.</t>
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Use 'Defects' sheet for all entries. Add extra metrics/charts here if needed.</t>
         </is>
       </c>
     </row>
